--- a/output/pdf_financials_xlsx/APLI.xlsx
+++ b/output/pdf_financials_xlsx/APLI.xlsx
@@ -810,19 +810,19 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.116953</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.03373</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.029882</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.016812</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>3.6e-05</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1356,19 +1356,19 @@
         <v>-5.416496</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-14.325112</v>
+        <v>-14.442065</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-25.07984</v>
+        <v>-25.11357</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-9.206621999999999</v>
+        <v>-9.236504</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.711327</v>
+        <v>-3.728139</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.605862</v>
+        <v>-2.605898</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-4.135388</v>
@@ -1424,19 +1424,19 @@
         <v>-5.416496</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-14.325112</v>
+        <v>-14.442065</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-25.07984</v>
+        <v>-25.11357</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-9.206621999999999</v>
+        <v>-9.236504</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.711327</v>
+        <v>-3.728139</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.605862</v>
+        <v>-2.605898</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-4.135388</v>
@@ -1467,16 +1467,16 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1803.417598821874</v>
+        <v>-1805.84302400833</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-2755.013660425463</v>
+        <v>-2763.955628304761</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-448.5491420788076</v>
+        <v>-450.5810320676523</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-2594.36894557112</v>
+        <v>-2594.4047867945</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>-1693.588719750675</v>
@@ -1570,31 +1570,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.721504</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.421097</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>10.50963</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>11.062938</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.664855</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.465882</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.09449299999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.228244</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.040003</v>
       </c>
     </row>
     <row r="35">
@@ -1638,31 +1638,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.030316</v>
+        <v>5.75182</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.030481</v>
+        <v>5.451578</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.030535</v>
+        <v>10.540165</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>5.061853</v>
+        <v>16.124791</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.664855</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.465882</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.09449299999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.228244</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.040003</v>
       </c>
     </row>
     <row r="37">
@@ -2046,31 +2046,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.86994</v>
+        <v>0.148436</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.049439</v>
+        <v>0.628342</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>10.865779</v>
+        <v>0.356149</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>12.165152</v>
+        <v>1.102214</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.772801</v>
+        <v>1.107946</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.997781</v>
+        <v>0.531899</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.302226</v>
+        <v>0.207733</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.355258</v>
+        <v>0.127014</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.171606</v>
+        <v>0.131603</v>
       </c>
     </row>
     <row r="49">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">

--- a/output/pdf_financials_xlsx/APLI.xlsx
+++ b/output/pdf_financials_xlsx/APLI.xlsx
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.017669</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.020714</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.976115</v>
+        <v>-3.958446</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.330984</v>
+        <v>-4.31027</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.416496</v>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.017669</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.020714</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -4264,22 +4264,22 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.0009120000000000001</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.001929</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.000103</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.024546</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.000654</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -14502,7 +14502,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -15601,7 +15605,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -17708,7 +17716,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E213" s="5" t="n">
         <v>0.017669</v>
       </c>

--- a/output/pdf_financials_xlsx/APLI.xlsx
+++ b/output/pdf_financials_xlsx/APLI.xlsx
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>0.002084</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>0.129686</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.13077</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.007642</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>0.073197</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>0.002427</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>0.08283699999999999</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
@@ -2370,25 +2370,25 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>0.001172</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.049706</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.06746000000000001</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.007539</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.048651</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>0.001904</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>0.052695</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>0</v>
@@ -4057,31 +4057,31 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.171283</v>
+        <v>-3.304178</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.549623</v>
+        <v>-3.457082</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.236275</v>
+        <v>-4.260309</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>2.348872</v>
+        <v>-11.45065</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>2.492742</v>
+        <v>-19.081182</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-3.811635</v>
+        <v>-10.097836</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.337276</v>
+        <v>-2.464425</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.306911</v>
+        <v>0.868816</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>2.100566</v>
+        <v>-1.337412</v>
       </c>
     </row>
     <row r="107">
@@ -13453,7 +13453,11 @@
           <t>Net changes in non-cash operating working capital total</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="n">
         <v>-3.304178</v>
       </c>
@@ -16498,7 +16502,11 @@
           <t>Proceeds from the issuance of Class A common shares in a private placement</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
